--- a/Laboratorio_Pesquisador_Base_Dados.xlsx
+++ b/Laboratorio_Pesquisador_Base_Dados.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opcoes_Globais" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opcoes_Especificas" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucoes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procedimentos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armadilhas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -106,6 +108,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5382,4 +5385,350 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Manipulação de uma variável independente, com grupo(s) de comparação e, quando possível, randomização.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Observacional</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Observacional</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Observa e mede variáveis como se apresentam, sem manipular a exposição ou intervenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Qualitativo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Qualitativo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Procedimentos de coleta e análise voltados à compreensão de significados (entrevistas, observação participante, análise de conteúdo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Misto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Misto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Combina procedimentos quantitativos e qualitativos, com estratégia explícita de integração.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>correta</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>explicacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Formular a hipótese depois de já conhecer os resultados (HARKing) deixa o artigo mais coerente e por isso é uma boa prática.</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HARKing (Hypothesizing After Results are Known) é considerado um viés de má prática: apresenta como confirmatório algo que foi, na verdade, exploratório, distorcendo a leitura do rigor do estudo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Grupo controle e randomização ajudam a reduzir vieses de seleção em estudos experimentais.</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Correto. Randomização e grupo controle são os principais mecanismos para equilibrar características entre grupos e isolar o efeito da variável independente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Excluir da análise, sem critério pré-definido, os participantes cujos dados "atrapalham" o resultado esperado não compromete a validade do estudo.</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Excluir casos post-hoc sem critério declarado é uma forma de viés de seleção/relato (data dredging) e compromete diretamente o controle de viés e a credibilidade dos achados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Usar um instrumento de coleta já validado na literatura aumenta a confiabilidade da mensuração.</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Correto. Instrumentos validados reduzem erros de mensuração e permitem comparação com outros estudos que usaram o mesmo instrumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Uma amostra grande garante, por si só, que os resultados sejam generalizáveis e livres de viés.</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Amostra grande reduz o erro amostral, mas não corrige viés de seleção: uma amostra grande e enviesada continua enviesada, apenas com mais precisão em torno do erro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>a6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cegar (blinding) o avaliador em relação ao grupo do participante ajuda a reduzir o viés de expectativa na coleta de dados.</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Correto. Quando quem avalia o desfecho não sabe a qual grupo o participante pertence, reduz-se a influência das expectativas do avaliador sobre o resultado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>a7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Encontrar correlação entre duas variáveis já é suficiente para afirmar que uma causa a outra.</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Correlação não implica causalidade. Para inferir causa é preciso desenho experimental, controle de confundidores, temporalidade adequada e plausibilidade teórica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Registrar previamente (pré-registro) as hipóteses e a análise planejada aumenta a transparência e reduz o risco de p-hacking.</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Correto. O pré-registro impede alterar hipóteses ou análises depois de ver os dados, protegendo contra achados exploratórios apresentados como se fossem confirmatórios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>a9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Testar várias análises estatísticas diferentes até achar uma significativa (p&lt;0,05) e reportar apenas essa é uma prática estatística aceitável.</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Isso é p-hacking: aumenta artificialmente a chance de um falso positivo e compromete seriamente a validade dos achados relatados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>a10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Declarar conflitos de interesse e fontes de financiamento faz parte do rigor ético e metodológico de uma pesquisa.</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Correto. A transparência sobre conflitos de interesse permite ao leitor avaliar possíveis influências nos resultados e nas conclusões apresentadas.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Laboratorio_Pesquisador_Base_Dados.xlsx
+++ b/Laboratorio_Pesquisador_Base_Dados.xlsx
@@ -575,8 +575,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Laboratório do Pesquisador – Delineamentos
-Simulador interativo | Prof. Mário César Nascimento, PhD © 2026</t>
+          <t>Laboratório do Pesquisador - Delineamentos</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -593,7 +592,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Parecer Técnico de Avaliação Metodológica – Laboratório do Pesquisador</t>
+          <t>Relatório de Delineamento Metodológico</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -603,36 +602,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>limite_erros_ajuda</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Quantidade de erros consecutivos para ativar ajuda extra do Orientador</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rodape_linha2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Simuladores interativos utilizados nas disciplinas de Ética e Pesquisa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Segunda linha do rodapé da exportação</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>limite_rigor_ajuda</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Abaixo deste % de Rigor o Orientador intensifica a ajuda</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rodape_linha3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Mário César Nascimento ©</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Terceira linha do rodapé da exportação</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4096,16 +4095,6 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>feedback_orientador_ajuda</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>e_armadilha</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>ativo</t>
         </is>
       </c>
@@ -4151,15 +4140,7 @@
           <t>Você escolheu a natureza exploratória. Ela é adequada quando o problema ainda não está claramente delimitado.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Lembre-se: a exploratória é o ponto de partida quando ainda sabemos pouco sobre o fenômeno. Se sua pergunta já busca relações de causa e efeito, talvez precise de outra natureza.</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="b">
+      <c r="K2" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4204,15 +4185,7 @@
           <t>Natureza descritiva escolhida. Boa opção quando o foco é caracterizar, mapear ou traçar o perfil de um fenômeno.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>A descritiva responde 'como é' ou 'quais são as características'. Se sua pergunta busca 'por que acontece' ou 'qual o efeito de X sobre Y', considere a explicativa.</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="b">
+      <c r="K3" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4257,15 +4230,7 @@
           <t>Natureza explicativa selecionada. Adequada quando o objetivo é compreender relações de causa e efeito.</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>A explicativa exige maior rigor de controle de variáveis. Verifique se seu delineamento (Fase 3) consegue sustentar uma pretensão causal.</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3" t="b">
+      <c r="K4" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4310,15 +4275,7 @@
           <t>Finalidade básica escolhida. O foco está na geração de conhecimento teórico.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Pesquisa básica não significa 'menos importante'. Ela fundamenta as pesquisas aplicadas futuras.</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="b">
+      <c r="K5" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4363,15 +4320,7 @@
           <t>Finalidade aplicada selecionada. O projeto busca resolver um problema concreto da Educação Física.</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Na pesquisa aplicada, a utilidade prática dos resultados deve estar clara desde a formulação do problema.</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="b">
+      <c r="K6" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4416,15 +4365,7 @@
           <t>Abordagem quantitativa escolhida. Adequada para medir magnitude, comparar grupos e testar hipóteses.</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Se sua pergunta busca compreender significados, experiências ou processos subjetivos, a abordagem qualitativa pode ser mais coerente.</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="b">
+      <c r="K7" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4469,15 +4410,7 @@
           <t>Abordagem qualitativa selecionada. Foco na compreensão profunda do fenômeno.</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Na qualitativa, a generalização estatística não é o objetivo. O valor está na profundidade e na interpretação do contexto.</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="b">
+      <c r="K8" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4522,15 +4455,7 @@
           <t>Abordagem mista escolhida. Exige clareza sobre como as duas vertentes se integram.</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Na abordagem mista, é fundamental justificar por que as duas abordagens são necessárias e como os dados serão integrados.</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="b">
+      <c r="K9" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4575,15 +4500,7 @@
           <t>Método dedutivo selecionado. Você partirá de uma teoria ou framework para testar hipóteses específicas.</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>O dedutivo exige que a teoria de partida esteja bem fundamentada. Verifique se há base teórica suficiente.</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="b">
+      <c r="K10" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4628,15 +4545,7 @@
           <t>Método indutivo escolhido. Você partirá dos dados para construir compreensões mais amplas.</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>No indutivo, evite generalizações apressadas. A qualidade da indução depende da riqueza e diversidade dos dados.</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="b">
+      <c r="K11" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4681,15 +4590,7 @@
           <t>Método dialético selecionado. Adequado para análises que consideram contradições e transformação social.</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>O dialético exige olhar histórico e relacional. Não se limita a descrever o fenômeno isoladamente.</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="b">
+      <c r="K12" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4734,15 +4635,7 @@
           <t>Método fenomenológico escolhido. Foco na experiência vivida e em seus significados.</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>Na fenomenologia, a qualidade da descrição e a redução fenomenológica são centrais. O número de participantes costuma ser reduzido e intencional.</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="b">
+      <c r="K13" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4787,15 +4680,7 @@
           <t>Temporalidade transversal escolhida. Adequada para diagnósticos e estudos de prevalência.</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>Atenção: estudos transversais têm dificuldade de estabelecer relação de causa e efeito, pois não garantem que a exposição antecedeu o desfecho.</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="b">
+      <c r="K14" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4840,15 +4725,7 @@
           <t>Temporalidade longitudinal selecionada. Fortalece a possibilidade de análises temporais e de mudança.</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>Estudos longitudinais exigem maior tempo, recursos e estratégias para lidar com perdas de seguimento (attrition).</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="b">
+      <c r="K15" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4893,15 +4770,7 @@
           <t>Desenho de coorte escolhido. Adequado para investigar incidência e fatores de risco.</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>Coortes bem conduzidas têm bom potencial de evidência, mas são mais complexas e custosas.</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="b">
+      <c r="K16" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4946,15 +4815,7 @@
           <t>Você priorizou a validade interna. Isso fortalece a confiança de que os resultados realmente se devem ao que foi investigado.</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>Priorizar validade interna é fundamental em estudos que pretendem estabelecer relações causais. Porém, excesso de controle pode reduzir a validade externa.</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="b">
+      <c r="K17" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4999,15 +4860,7 @@
           <t>Você priorizou a validade externa. Isso amplia a possibilidade de aplicar os resultados em outros contextos.</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Cuidado: buscar alta validade externa sem controle de vieses pode gerar resultados generalizáveis, porém pouco confiáveis.</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="b">
+      <c r="K18" s="3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5052,15 +4905,7 @@
           <t>Escolha equilibrada. Demonstra consciência de que validade interna e externa precisam ser ponderadas conforme o objetivo da pesquisa.</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>O equilíbrio não significa 'meio-termo fraco'. Significa justificar conscientemente as decisões de controle e de amostragem.</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3" t="b">
+      <c r="K19" s="3" t="b">
         <v>1</v>
       </c>
     </row>
